--- a/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
+++ b/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kryasolutions-my.sharepoint.com/personal/sivakumar_mani_kryasolutions_com/Documents/01Aws_workspace/TCV_Core/comparison_reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC2A5D24-5B0A-4519-A2D8-2D0CF1EFE9C4}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{132A24A6-ED42-4A14-8123-8BD7AA821F30}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="433">
   <si>
     <t>Customers in Excel but Not Available in Database</t>
   </si>
@@ -1319,13 +1319,16 @@
   </si>
   <si>
     <t>Dilipkumar  Rajamani</t>
+  </si>
+  <si>
+    <t>double entry</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1345,8 +1348,15 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1381,6 +1391,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1394,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1404,6 +1432,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1706,7 +1738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -2575,20 +2607,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52">
+    <row r="52" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="7">
         <v>246</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2609,20 +2641,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54">
+    <row r="54" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="7">
         <v>257</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2694,20 +2726,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59">
+    <row r="59" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="7">
         <v>282</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2728,20 +2760,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61">
+    <row r="61" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="7">
         <v>287</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2779,20 +2811,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64">
+    <row r="64" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="7">
         <v>292</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2830,20 +2862,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67">
+    <row r="67" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="6">
         <v>305</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2864,54 +2896,54 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69">
+    <row r="69" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="6">
         <v>308</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70">
+      <c r="E69" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="5">
         <v>315</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71">
+      <c r="E70" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="5">
         <v>317</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2949,20 +2981,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74">
+    <row r="74" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="5">
         <v>338</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2983,20 +3015,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76">
+    <row r="76" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="5">
         <v>341</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3034,37 +3066,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79">
+    <row r="79" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="5">
         <v>361</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E79" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80">
+      <c r="E79" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="5">
         <v>364</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3085,20 +3117,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82">
+    <row r="82" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="5">
         <v>371</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3153,20 +3185,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86">
+    <row r="86" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="8">
         <v>383</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3187,37 +3219,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88">
+    <row r="88" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="9">
         <v>385</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E88" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89">
+      <c r="E88" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="9">
         <v>386</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3255,20 +3287,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92">
+    <row r="92" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="9">
         <v>389</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3476,37 +3508,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105">
+    <row r="105" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="6">
         <v>402</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="E105" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106">
+      <c r="E105" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="6">
         <v>403</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3561,20 +3593,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110">
+    <row r="110" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="6">
         <v>407</v>
       </c>
-      <c r="B110" t="s">
-        <v>218</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="B110" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3663,37 +3695,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A116">
+    <row r="116" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="6">
         <v>414</v>
       </c>
-      <c r="B116" t="s">
-        <v>218</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="B116" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="E116" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A117">
+      <c r="E116" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="6">
         <v>415</v>
       </c>
-      <c r="B117" t="s">
-        <v>218</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B117" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3799,20 +3831,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A124">
+    <row r="124" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="6">
         <v>423</v>
       </c>
-      <c r="B124" t="s">
-        <v>218</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B124" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C124" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3867,20 +3899,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128">
+    <row r="128" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="10">
         <v>427</v>
       </c>
-      <c r="B128" t="s">
-        <v>218</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="B128" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C128" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4105,20 +4137,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A142">
+    <row r="142" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="6">
         <v>441</v>
       </c>
-      <c r="B142" t="s">
-        <v>218</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="B142" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4156,7 +4188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>444</v>
       </c>
@@ -4173,7 +4205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>445</v>
       </c>
@@ -4190,7 +4222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>446</v>
       </c>
@@ -4207,7 +4239,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>447</v>
       </c>
@@ -4224,7 +4256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>448</v>
       </c>
@@ -4241,7 +4273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>449</v>
       </c>
@@ -4258,7 +4290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>450</v>
       </c>
@@ -4275,7 +4307,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>451</v>
       </c>
@@ -4292,7 +4324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>452</v>
       </c>
@@ -4309,7 +4341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>453</v>
       </c>
@@ -4326,24 +4358,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A155">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A155" s="6">
         <v>454</v>
       </c>
-      <c r="B155" t="s">
-        <v>218</v>
-      </c>
-      <c r="C155" t="s">
+      <c r="B155" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C155" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D155" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="E155" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E155" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>455</v>
       </c>
@@ -4360,24 +4392,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A157" s="6">
         <v>456</v>
       </c>
-      <c r="B157" t="s">
-        <v>218</v>
-      </c>
-      <c r="C157" t="s">
+      <c r="B157" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C157" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D157" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="E157" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E157" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4">
         <v>457</v>
       </c>
@@ -4394,7 +4426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>458</v>
       </c>
@@ -4411,24 +4443,28 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A160">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A160" s="10">
         <v>459</v>
       </c>
-      <c r="B160" t="s">
-        <v>218</v>
-      </c>
-      <c r="C160" t="s">
+      <c r="B160" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C160" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D160" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="E160" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E160" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="G160" s="10"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>461</v>
       </c>
@@ -4445,24 +4481,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A162" s="10">
         <v>462</v>
       </c>
-      <c r="B162" t="s">
-        <v>218</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="B162" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C162" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D162" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="E162" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E162" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="10"/>
+      <c r="G162" s="10"/>
+      <c r="H162" s="10"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>463</v>
       </c>
@@ -4479,7 +4518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>464</v>
       </c>
@@ -4496,7 +4535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>465</v>
       </c>
@@ -4513,7 +4552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>467</v>
       </c>
@@ -4530,7 +4569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>468</v>
       </c>
@@ -4547,7 +4586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>469</v>
       </c>
@@ -4564,7 +4603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>470</v>
       </c>
@@ -4581,7 +4620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>471</v>
       </c>
@@ -4598,7 +4637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>472</v>
       </c>
@@ -4615,7 +4654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>473</v>
       </c>
@@ -4632,7 +4671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>474</v>
       </c>
@@ -4649,24 +4688,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A174">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A174" s="6">
         <v>475</v>
       </c>
-      <c r="B174" t="s">
-        <v>218</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="B174" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C174" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D174" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="E174" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E174" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>476</v>
       </c>
@@ -4683,7 +4722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>477</v>
       </c>
@@ -4752,19 +4791,19 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A180">
+      <c r="A180" s="6">
         <v>481</v>
       </c>
-      <c r="B180" t="s">
-        <v>218</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="B180" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C180" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5126,19 +5165,19 @@
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A202">
+      <c r="A202" s="6">
         <v>504</v>
       </c>
-      <c r="B202" t="s">
-        <v>218</v>
-      </c>
-      <c r="C202" t="s">
+      <c r="B202" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C202" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="D202" t="s">
+      <c r="D202" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E202" s="6" t="s">
         <v>9</v>
       </c>
     </row>

--- a/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
+++ b/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kryasolutions-my.sharepoint.com/personal/sivakumar_mani_kryasolutions_com/Documents/01Aws_workspace/TCV_Core/comparison_reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{132A24A6-ED42-4A14-8123-8BD7AA821F30}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12981026-47DE-479A-8250-737DBFC9EACA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1425,10 +1425,6 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -1436,6 +1432,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1749,13 +1749,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1775,1532 +1775,1532 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>41</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>43</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>45</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>49</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>54</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>55</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>56</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>64</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>65</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>66</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <v>68</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <v>69</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>70</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>73</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <v>78</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>81</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>88</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>101</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <v>111</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <v>117</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="B24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <v>123</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <v>125</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
         <v>126</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
         <v>143</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
         <v>144</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <v>147</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="B30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="4">
+      <c r="A31" s="2">
         <v>154</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>155</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="B32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="4">
+      <c r="A33" s="2">
         <v>159</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="B33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="4">
+      <c r="A34" s="2">
         <v>168</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="4">
+      <c r="A35" s="2">
         <v>173</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="4" t="s">
+      <c r="B35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="4">
+      <c r="A36" s="2">
         <v>176</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="B36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="4">
+      <c r="A37" s="2">
         <v>192</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="B37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="4">
+      <c r="A38" s="2">
         <v>205</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="4" t="s">
+      <c r="B38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="5">
+      <c r="E38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
         <v>215</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="4">
+      <c r="A40" s="2">
         <v>217</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="4" t="s">
+      <c r="B40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5">
+      <c r="E40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
         <v>221</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="4">
+      <c r="A42" s="2">
         <v>224</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="4" t="s">
+      <c r="B42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="4">
+      <c r="A43" s="2">
         <v>225</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="4" t="s">
+      <c r="B43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="4">
+      <c r="A44" s="2">
         <v>226</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="4" t="s">
+      <c r="B44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="4">
+      <c r="A45" s="2">
         <v>227</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="4" t="s">
+      <c r="B45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="4">
+      <c r="A46" s="2">
         <v>231</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="4" t="s">
+      <c r="B46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="5">
+      <c r="E46" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="3">
         <v>233</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="4">
+      <c r="A48" s="2">
         <v>237</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="4" t="s">
+      <c r="B48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="4">
+      <c r="A49" s="2">
         <v>240</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="4" t="s">
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="4">
+      <c r="A50" s="2">
         <v>241</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="B50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="6">
+      <c r="E50" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="5">
         <v>243</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="7">
+      <c r="E51" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="5">
         <v>246</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="4">
+      <c r="A53" s="2">
         <v>249</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="4" t="s">
+      <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="7">
+      <c r="E53" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="5">
         <v>257</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="4">
+      <c r="A55" s="2">
         <v>259</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="4" t="s">
+      <c r="B55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="4">
+      <c r="A56" s="2">
         <v>274</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="4" t="s">
+      <c r="B56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="4">
+      <c r="A57" s="2">
         <v>275</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="4" t="s">
+      <c r="B57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="4">
+      <c r="A58" s="2">
         <v>278</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="4" t="s">
+      <c r="B58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="7">
+      <c r="E58" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="5">
         <v>282</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="4">
+      <c r="A60" s="2">
         <v>283</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="4" t="s">
+      <c r="B60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="7">
+      <c r="E60" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="5">
         <v>287</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="4">
+      <c r="A62" s="2">
         <v>290</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="4" t="s">
+      <c r="B62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="4">
+      <c r="A63" s="2">
         <v>291</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="4" t="s">
+      <c r="B63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="7">
+      <c r="E63" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5">
         <v>292</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="4">
+      <c r="A65" s="2">
         <v>296</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="4" t="s">
+      <c r="B65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="4">
+      <c r="A66" s="2">
         <v>304</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="4" t="s">
+      <c r="B66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="6">
+      <c r="E66" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
         <v>305</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="4">
+      <c r="A68" s="2">
         <v>306</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="4" t="s">
+      <c r="B68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="6">
+      <c r="E68" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
         <v>308</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="5">
+      <c r="E69" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="3">
         <v>315</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="5">
+      <c r="E70" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="3">
         <v>317</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="4">
+      <c r="A72" s="2">
         <v>325</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="4" t="s">
+      <c r="B72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="4">
+      <c r="A73" s="2">
         <v>328</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="4" t="s">
+      <c r="B73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E73" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="5">
+      <c r="E73" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3">
         <v>338</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="4">
+      <c r="A75" s="2">
         <v>340</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="4" t="s">
+      <c r="B75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="5">
+      <c r="E75" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="3">
         <v>341</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="4">
+      <c r="A77" s="2">
         <v>344</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="4" t="s">
+      <c r="B77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" s="4">
+      <c r="A78" s="2">
         <v>345</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="4" t="s">
+      <c r="B78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="5">
+      <c r="E78" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="3">
         <v>361</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E79" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="5">
+      <c r="E79" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="3">
         <v>364</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="4">
+      <c r="A81" s="2">
         <v>369</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="4" t="s">
+      <c r="B81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="5">
+      <c r="E81" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="3">
         <v>371</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" s="4">
+      <c r="A83" s="2">
         <v>372</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="4" t="s">
+      <c r="B83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="4">
+      <c r="A84" s="2">
         <v>375</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="4" t="s">
+      <c r="B84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E84" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="4">
+      <c r="A85" s="2">
         <v>382</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="4" t="s">
+      <c r="B85" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="8">
+      <c r="E85" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="6">
         <v>383</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D86" s="8" t="s">
+      <c r="D86" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="4">
+      <c r="A87" s="2">
         <v>384</v>
       </c>
-      <c r="B87" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" s="4" t="s">
+      <c r="B87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="9">
+      <c r="E87" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="7">
         <v>385</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D88" s="9" t="s">
+      <c r="D88" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E88" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="9">
+      <c r="E88" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="7">
         <v>386</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="D89" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="4">
+      <c r="A90" s="2">
         <v>387</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="4" t="s">
+      <c r="B90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E90" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="4">
+      <c r="A91" s="2">
         <v>388</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="4" t="s">
+      <c r="B91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E91" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="9">
+      <c r="E91" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="7">
         <v>389</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D92" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="E92" s="9" t="s">
+      <c r="E92" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3390,36 +3390,36 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="4">
+      <c r="A98" s="2">
         <v>395</v>
       </c>
-      <c r="B98" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="4" t="s">
+      <c r="B98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="E98" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" s="4">
+      <c r="A99" s="2">
         <v>396</v>
       </c>
-      <c r="B99" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="4" t="s">
+      <c r="B99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="E99" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3475,19 +3475,19 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A103" s="4">
+      <c r="A103" s="2">
         <v>400</v>
       </c>
-      <c r="B103" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="4" t="s">
+      <c r="B103" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="E103" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3508,37 +3508,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="6">
+    <row r="105" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="4">
         <v>402</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E105" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="6">
+      <c r="E105" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="4">
         <v>403</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C106" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E106" s="6" t="s">
+      <c r="E106" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3593,20 +3593,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="6">
+    <row r="110" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="4">
         <v>407</v>
       </c>
-      <c r="B110" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C110" s="6" t="s">
+      <c r="B110" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E110" s="6" t="s">
+      <c r="E110" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3695,37 +3695,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="6">
+    <row r="116" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="4">
         <v>414</v>
       </c>
-      <c r="B116" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C116" s="6" t="s">
+      <c r="B116" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E116" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="6">
+      <c r="E116" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="4">
         <v>415</v>
       </c>
-      <c r="B117" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C117" s="6" t="s">
+      <c r="B117" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E117" s="6" t="s">
+      <c r="E117" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3831,20 +3831,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="6">
+    <row r="124" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="4">
         <v>423</v>
       </c>
-      <c r="B124" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C124" s="6" t="s">
+      <c r="B124" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E124" s="6" t="s">
+      <c r="E124" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3899,20 +3899,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="10">
+    <row r="128" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="8">
         <v>427</v>
       </c>
-      <c r="B128" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="C128" s="10" t="s">
+      <c r="B128" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C128" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E128" s="10" t="s">
+      <c r="E128" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3985,36 +3985,36 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" s="4">
+      <c r="A133" s="2">
         <v>432</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="D133" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E133" s="4" t="s">
+      <c r="E133" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A134" s="4">
+      <c r="A134" s="2">
         <v>433</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D134" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E134" s="4" t="s">
+      <c r="E134" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4104,53 +4104,53 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A140" s="4">
+      <c r="A140" s="2">
         <v>439</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="E140" s="4" t="s">
+      <c r="E140" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A141" s="4">
+      <c r="A141" s="2">
         <v>440</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D141" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E141" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="6">
+      <c r="E141" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="4">
         <v>441</v>
       </c>
-      <c r="B142" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C142" s="6" t="s">
+      <c r="B142" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="D142" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E142" s="6" t="s">
+      <c r="E142" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4172,19 +4172,19 @@
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A144" s="4">
+      <c r="A144" s="2">
         <v>443</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="D144" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E144" s="4" t="s">
+      <c r="E144" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4359,19 +4359,19 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A155" s="6">
+      <c r="A155" s="4">
         <v>454</v>
       </c>
-      <c r="B155" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C155" s="6" t="s">
+      <c r="B155" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D155" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="E155" s="6" t="s">
+      <c r="E155" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4393,36 +4393,36 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A157" s="6">
+      <c r="A157" s="4">
         <v>456</v>
       </c>
-      <c r="B157" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C157" s="6" t="s">
+      <c r="B157" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C157" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="D157" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E157" s="6" t="s">
+      <c r="E157" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A158" s="4">
+      <c r="A158" s="2">
         <v>457</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D158" s="4" t="s">
+      <c r="D158" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E158" s="4" t="s">
+      <c r="E158" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4444,25 +4444,25 @@
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A160" s="10">
+      <c r="A160" s="8">
         <v>459</v>
       </c>
-      <c r="B160" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="C160" s="10" t="s">
+      <c r="B160" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C160" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="D160" s="10" t="s">
+      <c r="D160" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="E160" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" s="10" t="s">
+      <c r="E160" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="G160" s="10"/>
+      <c r="G160" s="8"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161">
@@ -4482,24 +4482,24 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A162" s="10">
+      <c r="A162" s="8">
         <v>462</v>
       </c>
-      <c r="B162" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="C162" s="10" t="s">
+      <c r="B162" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C162" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="D162" s="10" t="s">
+      <c r="D162" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="E162" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" s="10"/>
-      <c r="G162" s="10"/>
-      <c r="H162" s="10"/>
+      <c r="E162" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="8"/>
+      <c r="G162" s="8"/>
+      <c r="H162" s="8"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163">
@@ -4689,19 +4689,19 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A174" s="6">
+      <c r="A174" s="4">
         <v>475</v>
       </c>
-      <c r="B174" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C174" s="6" t="s">
+      <c r="B174" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="D174" s="6" t="s">
+      <c r="D174" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="E174" s="6" t="s">
+      <c r="E174" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4791,19 +4791,19 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A180" s="6">
+      <c r="A180" s="4">
         <v>481</v>
       </c>
-      <c r="B180" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C180" s="6" t="s">
+      <c r="B180" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C180" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="D180" s="6" t="s">
+      <c r="D180" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E180" s="6" t="s">
+      <c r="E180" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5165,36 +5165,36 @@
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A202" s="6">
+      <c r="A202" s="4">
         <v>504</v>
       </c>
-      <c r="B202" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C202" s="6" t="s">
+      <c r="B202" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="D202" s="6" t="s">
+      <c r="D202" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="E202" s="6" t="s">
+      <c r="E202" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A203" s="4">
+      <c r="A203" s="2">
         <v>505</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D203" s="4" t="s">
+      <c r="D203" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E203" s="4" t="s">
+      <c r="E203" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5233,19 +5233,19 @@
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A206" s="4">
+      <c r="A206" s="2">
         <v>509</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D206" s="4" t="s">
+      <c r="D206" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="E206" s="4" t="s">
+      <c r="E206" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5267,104 +5267,104 @@
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A208" s="4">
+      <c r="A208" s="2">
         <v>511</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C208" s="4" t="s">
+      <c r="C208" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D208" s="4" t="s">
+      <c r="D208" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="E208" s="4" t="s">
+      <c r="E208" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A209" s="4">
+      <c r="A209" s="2">
         <v>512</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C209" s="4" t="s">
+      <c r="C209" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D209" s="4" t="s">
+      <c r="D209" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E209" s="4" t="s">
+      <c r="E209" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A210" s="4">
+      <c r="A210" s="2">
         <v>513</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D210" s="4" t="s">
+      <c r="D210" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E210" s="4" t="s">
+      <c r="E210" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A211" s="4">
+      <c r="A211" s="2">
         <v>514</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D211" s="4" t="s">
+      <c r="D211" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E211" s="4" t="s">
+      <c r="E211" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A212" s="4">
+      <c r="A212" s="2">
         <v>515</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D212" s="4" t="s">
+      <c r="D212" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E212" s="4" t="s">
+      <c r="E212" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A213" s="4">
+      <c r="A213" s="2">
         <v>517</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="B213" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C213" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D213" s="4" t="s">
+      <c r="D213" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E213" s="4" t="s">
+      <c r="E213" s="2" t="s">
         <v>9</v>
       </c>
     </row>

--- a/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
+++ b/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kryasolutions-my.sharepoint.com/personal/sivakumar_mani_kryasolutions_com/Documents/01Aws_workspace/TCV_Core/comparison_reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12981026-47DE-479A-8250-737DBFC9EACA}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D69E922-D5CD-49B0-B96D-8D27BE1CAAB5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2863,19 +2863,19 @@
       </c>
     </row>
     <row r="67" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="4">
+      <c r="A67" s="5">
         <v>305</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="5" t="s">
         <v>9</v>
       </c>
     </row>

--- a/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
+++ b/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kryasolutions-my.sharepoint.com/personal/sivakumar_mani_kryasolutions_com/Documents/01Aws_workspace/TCV_Core/comparison_reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D69E922-D5CD-49B0-B96D-8D27BE1CAAB5}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47FCD821-7344-416E-86FE-5FC81E3AB581}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2896,20 +2896,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="4">
+    <row r="69" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="5">
         <v>308</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3508,37 +3508,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="4">
+    <row r="105" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="5">
         <v>402</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="E105" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="4">
+      <c r="E105" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="5">
         <v>403</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E106" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3593,20 +3593,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="4">
+    <row r="110" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="5">
         <v>407</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C110" s="4" t="s">
+      <c r="B110" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3695,37 +3695,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="4">
+    <row r="116" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="5">
         <v>414</v>
       </c>
-      <c r="B116" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C116" s="4" t="s">
+      <c r="B116" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="4">
+      <c r="E116" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="5">
         <v>415</v>
       </c>
-      <c r="B117" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C117" s="4" t="s">
+      <c r="B117" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="E117" s="4" t="s">
+      <c r="E117" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3831,20 +3831,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="4">
+    <row r="124" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="5">
         <v>423</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C124" s="4" t="s">
+      <c r="B124" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C124" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="D124" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E124" s="4" t="s">
+      <c r="E124" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4137,20 +4137,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="4">
+    <row r="142" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="5">
         <v>441</v>
       </c>
-      <c r="B142" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C142" s="4" t="s">
+      <c r="B142" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D142" s="4" t="s">
+      <c r="D142" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="E142" s="4" t="s">
+      <c r="E142" s="5" t="s">
         <v>9</v>
       </c>
     </row>

--- a/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
+++ b/comparison_reports/02_Customers_Not_Available_in_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kryasolutions-my.sharepoint.com/personal/sivakumar_mani_kryasolutions_com/Documents/01Aws_workspace/TCV_Core/comparison_reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47FCD821-7344-416E-86FE-5FC81E3AB581}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_67B9A47F95AF1D5E82F4D3125D5ED87656CC47E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79C8B317-C1A7-4440-B902-368E95BB5515}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$2:$E$213</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -1356,7 +1356,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1409,6 +1409,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1422,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1436,6 +1442,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4359,19 +4366,19 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A155" s="4">
+      <c r="A155" s="11">
         <v>454</v>
       </c>
-      <c r="B155" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C155" s="4" t="s">
+      <c r="B155" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C155" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="E155" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4393,19 +4400,19 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A157" s="4">
+      <c r="A157" s="5">
         <v>456</v>
       </c>
-      <c r="B157" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C157" s="4" t="s">
+      <c r="B157" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="D157" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E157" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4689,19 +4696,19 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A174" s="4">
+      <c r="A174" s="5">
         <v>475</v>
       </c>
-      <c r="B174" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C174" s="4" t="s">
+      <c r="B174" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C174" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="D174" s="4" t="s">
+      <c r="D174" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="E174" s="4" t="s">
+      <c r="E174" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4791,19 +4798,19 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A180" s="4">
+      <c r="A180" s="5">
         <v>481</v>
       </c>
-      <c r="B180" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C180" s="4" t="s">
+      <c r="B180" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C180" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="D180" s="4" t="s">
+      <c r="D180" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E180" s="4" t="s">
+      <c r="E180" s="5" t="s">
         <v>9</v>
       </c>
     </row>
